--- a/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636075924</v>
+        <v>10.84497621036603</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907204137105</v>
+        <v>37.78907151732935</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.38118015115502</v>
+        <v>4.931318718431728</v>
       </c>
       <c r="C2" t="n">
-        <v>3.634430001121692</v>
+        <v>11.02699021410017</v>
       </c>
       <c r="D2" t="n">
-        <v>19.73312885536089</v>
+        <v>20.25443688631594</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.83330817892307</v>
+        <v>16.13993225781756</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0354660905399</v>
+        <v>24.58296251434013</v>
       </c>
       <c r="D3" t="n">
-        <v>52.77384784178729</v>
+        <v>71.82466204269666</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.45477983790708</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="C4" t="n">
-        <v>48.56215019056847</v>
+        <v>85.93139480501907</v>
       </c>
       <c r="D4" t="n">
-        <v>67.02980625515522</v>
+        <v>97.72414822843174</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.64179492779949</v>
+        <v>40.10439371848221</v>
       </c>
       <c r="C5" t="n">
-        <v>76.42905877561419</v>
+        <v>154.8952440375405</v>
       </c>
       <c r="D5" t="n">
-        <v>54.68334712654735</v>
+        <v>70.0722423906161</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.2655235151657</v>
+        <v>36.99127174831558</v>
       </c>
       <c r="C6" t="n">
-        <v>87.14483496746813</v>
+        <v>172.3173387971044</v>
       </c>
       <c r="D6" t="n">
-        <v>43.1095234411817</v>
+        <v>45.92713935237005</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.78845088416398</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>88.81184256927919</v>
+        <v>155.4656394537079</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.19455027635689</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>66.50849822420017</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -996,7 +996,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.707261267182968</v>
+        <v>7.634447478779168</v>
       </c>
       <c r="C21" t="n">
-        <v>95.37735818138924</v>
+        <v>92.56767568019741</v>
       </c>
       <c r="D21" t="n">
-        <v>8.67066892558084</v>
+        <v>7.634447478779168</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.12476407389735</v>
+        <v>5.990624491314037</v>
       </c>
       <c r="C2" t="n">
-        <v>3.968224220565608</v>
+        <v>10.78548027885546</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31570615460675</v>
+        <v>26.35599886820987</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.47282684501524</v>
+        <v>16.08102739556275</v>
       </c>
       <c r="C3" t="n">
-        <v>14.48568737616169</v>
+        <v>33.23706852727577</v>
       </c>
       <c r="D3" t="n">
-        <v>55.74854338565513</v>
+        <v>70.8821842466197</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.57040508282995</v>
+        <v>31.702596865538</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81892612072464</v>
+        <v>74.20245498238242</v>
       </c>
       <c r="D4" t="n">
-        <v>77.11235517776997</v>
+        <v>108.4193077184965</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.78400947619504</v>
+        <v>44.64497685062371</v>
       </c>
       <c r="C5" t="n">
-        <v>82.24591392327655</v>
+        <v>154.6498071114788</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59899893944014</v>
+        <v>84.23395302437635</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.68190771495337</v>
+        <v>44.07556318216056</v>
       </c>
       <c r="C6" t="n">
-        <v>104.2115370580947</v>
+        <v>205.243193302134</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11331156327844</v>
+        <v>55.2252718592916</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.26293812495145</v>
+        <v>33.95570784678443</v>
       </c>
       <c r="C7" t="n">
-        <v>106.7179389470368</v>
+        <v>195.4100082963978</v>
       </c>
       <c r="D7" t="n">
         <v>41.9206269713388</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.20837685967435</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>92.21065312138165</v>
+        <v>146.7860080004618</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>84.7562428030356</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.896800375492085</v>
+        <v>7.800350526554685</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6326049752701</v>
+        <v>100.4295130293916</v>
       </c>
       <c r="D21" t="n">
-        <v>9.871000469365107</v>
+        <v>8.775394342374021</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.51630148144259</v>
+        <v>5.861033794353459</v>
       </c>
       <c r="C2" t="n">
-        <v>4.997095814616265</v>
+        <v>15.48707003449343</v>
       </c>
       <c r="D2" t="n">
-        <v>27.25724326070844</v>
+        <v>24.05870924027233</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.73222922311465</v>
+        <v>17.28857707178633</v>
       </c>
       <c r="C3" t="n">
-        <v>14.84893402673301</v>
+        <v>36.62409810692726</v>
       </c>
       <c r="D3" t="n">
-        <v>58.59561172797088</v>
+        <v>73.27764864498192</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.21304891848411</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="C4" t="n">
-        <v>39.13049999586936</v>
+        <v>76.869863494821</v>
       </c>
       <c r="D4" t="n">
-        <v>84.43815654685966</v>
+        <v>114.2773962697372</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.87022334771952</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C5" t="n">
-        <v>80.57694282605698</v>
+        <v>145.2250291507094</v>
       </c>
       <c r="D5" t="n">
-        <v>75.47185476397355</v>
+        <v>98.37111996553043</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>81.46935148921733</v>
+        <v>49.99255659565609</v>
       </c>
       <c r="C6" t="n">
-        <v>115.441749046974</v>
+        <v>222.0683854575158</v>
       </c>
       <c r="D6" t="n">
-        <v>56.99634471775284</v>
+        <v>64.32214608684252</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>65.75549773504287</v>
+        <v>41.02232782195297</v>
       </c>
       <c r="C7" t="n">
-        <v>127.498592602829</v>
+        <v>234.3363047697839</v>
       </c>
       <c r="D7" t="n">
-        <v>46.23246288839079</v>
+        <v>46.17257627843174</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.47393176590651</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="C8" t="n">
-        <v>114.491417269263</v>
+        <v>190.7633964121977</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.74374815365835</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>85.42186774651495</v>
+        <v>122.8078020719377</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>66.62139921018856</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>30.10038461220721</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.072473468382391</v>
+        <v>7.949827979551473</v>
       </c>
       <c r="C21" t="n">
-        <v>113.0146285573535</v>
+        <v>107.3226777239449</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09965101902579</v>
+        <v>9.93728497443934</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.19486907152638</v>
+        <v>5.519385593275567</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2780555844801</v>
+        <v>10.90230825566083</v>
       </c>
       <c r="D2" t="n">
-        <v>22.03729071722815</v>
+        <v>20.09048501970673</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.62762418711675</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="C3" t="n">
-        <v>23.63066724122073</v>
+        <v>55.64545987670921</v>
       </c>
       <c r="D3" t="n">
-        <v>64.75607857211962</v>
+        <v>80.04679906576369</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.00814138573701</v>
+        <v>21.74767514447534</v>
       </c>
       <c r="C4" t="n">
-        <v>62.75429500316037</v>
+        <v>112.3374628061455</v>
       </c>
       <c r="D4" t="n">
-        <v>82.6769011654409</v>
+        <v>109.3509862898267</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.89670517353839</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>68.96777622333845</v>
+        <v>132.6832022289564</v>
       </c>
       <c r="D5" t="n">
-        <v>55.0515025156399</v>
+        <v>63.91177554646737</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>25.43904651244335</v>
       </c>
       <c r="C6" t="n">
-        <v>83.96495415341272</v>
+        <v>154.3248486213731</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.48795397120644</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>80.4876037849705</v>
+        <v>134.1460063082842</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>27.72750041104266</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>62.92021036517807</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>50.80937068558941</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
         <v>28.25371718051895</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>25.19753657719863</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.791730617979434</v>
+        <v>3.427281235525615</v>
       </c>
       <c r="C2" t="n">
-        <v>1.841758693167016</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>15.18076475076843</v>
+        <v>15.159166301275</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>38.23416434189203</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1917849596934</v>
+        <v>50.21148633370311</v>
       </c>
       <c r="D3" t="n">
-        <v>68.08420328951631</v>
+        <v>78.17166095065228</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.18301565027996</v>
+        <v>28.81822211046087</v>
       </c>
       <c r="C4" t="n">
-        <v>63.21375292874787</v>
+        <v>128.584405563726</v>
       </c>
       <c r="D4" t="n">
-        <v>94.11229842450773</v>
+        <v>122.343435407829</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>31.34229545807943</v>
       </c>
       <c r="C5" t="n">
-        <v>93.16785713302231</v>
+        <v>167.0198281849886</v>
       </c>
       <c r="D5" t="n">
-        <v>68.40327129339653</v>
+        <v>80.03698158872123</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.26802678992194</v>
+        <v>29.58496706747763</v>
       </c>
       <c r="C6" t="n">
-        <v>98.85806682683683</v>
+        <v>184.4330872152143</v>
       </c>
       <c r="D6" t="n">
-        <v>37.23278168356029</v>
+        <v>37.31328499530853</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.82920126165683</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>100.6095047312131</v>
+        <v>167.9819409351505</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>30.30262463928205</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>80.27750977626168</v>
+        <v>118.9141906768949</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>49.14530832689106</v>
+        <v>53.13905798776709</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.69788374899924</v>
+        <v>3.304562772494764</v>
       </c>
       <c r="C2" t="n">
-        <v>9.656470418971628</v>
+        <v>7.115707360380882</v>
       </c>
       <c r="D2" t="n">
-        <v>15.25243233317845</v>
+        <v>14.87740471015616</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.46363126277852</v>
+        <v>16.02212253330795</v>
       </c>
       <c r="C3" t="n">
-        <v>12.08531423927824</v>
+        <v>34.64096774434871</v>
       </c>
       <c r="D3" t="n">
-        <v>65.12914269973339</v>
+        <v>73.34146224575797</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.48627787990099</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="C4" t="n">
-        <v>53.64171281234147</v>
+        <v>128.0611340373625</v>
       </c>
       <c r="D4" t="n">
-        <v>105.573221123885</v>
+        <v>131.0476105536812</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.2245521534946</v>
+        <v>36.57010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>105.3906160508951</v>
+        <v>198.9757159582223</v>
       </c>
       <c r="D5" t="n">
-        <v>84.6757394912874</v>
+        <v>99.18106182153404</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.25043744670351</v>
+        <v>34.97868895460962</v>
       </c>
       <c r="C6" t="n">
-        <v>124.6593782421473</v>
+        <v>220.4985708784251</v>
       </c>
       <c r="D6" t="n">
-        <v>48.22148373719484</v>
+        <v>50.31456984264904</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.78278138211675</v>
+        <v>23.59532432386784</v>
       </c>
       <c r="C7" t="n">
-        <v>122.9472102459408</v>
+        <v>213.3161046741554</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.02627050830318</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>106.814150222053</v>
+        <v>163.9764103018235</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>90.63592980376974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
         <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>27.0569667290421</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.48354395430394</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.452225838759285</v>
+        <v>1.999820073550753</v>
       </c>
       <c r="C2" t="n">
-        <v>4.204825417289089</v>
+        <v>3.503857556456866</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4340146007351</v>
+        <v>10.50764567855361</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.39138284329177</v>
+        <v>15.71778074499143</v>
       </c>
       <c r="C3" t="n">
-        <v>24.96093538047515</v>
+        <v>34.04210164475816</v>
       </c>
       <c r="D3" t="n">
-        <v>64.79534848028949</v>
+        <v>71.91301933607886</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69.86313012961152</v>
+        <v>35.86324363613598</v>
       </c>
       <c r="C4" t="n">
-        <v>50.08091388903829</v>
+        <v>126.3764549768749</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1707866806018</v>
+        <v>138.9222088894449</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.16979526623503</v>
+        <v>37.77274292089604</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3005983617407</v>
+        <v>240.7245370813179</v>
       </c>
       <c r="D5" t="n">
-        <v>91.96521619531997</v>
+        <v>101.7336058525757</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.03909964838319</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>158.1085042735403</v>
+        <v>257.3690876591183</v>
       </c>
       <c r="D6" t="n">
-        <v>47.97997380195012</v>
+        <v>48.90576188705487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.57618809140164</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>135.104192067629</v>
+        <v>217.7477138111255</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>89.12305659152544</v>
+        <v>113.4065860560703</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
         <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77302065833652</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.6018524004323</v>
+        <v>2.370920705756047</v>
       </c>
       <c r="C2" t="n">
-        <v>3.621667280966483</v>
+        <v>7.486807992586176</v>
       </c>
       <c r="D2" t="n">
-        <v>14.02819294598267</v>
+        <v>14.59760661444582</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.34596040698915</v>
+        <v>11.55517047898496</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34181243199391</v>
+        <v>24.04791001552562</v>
       </c>
       <c r="D3" t="n">
-        <v>58.51707191163113</v>
+        <v>64.71189992542851</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>65.51104255668541</v>
+        <v>33.04268248183489</v>
       </c>
       <c r="C4" t="n">
-        <v>57.04935909378215</v>
+        <v>107.8705107518225</v>
       </c>
       <c r="D4" t="n">
-        <v>120.87572258998</v>
+        <v>142.0746007677814</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84.38121518001337</v>
+        <v>44.39953992456201</v>
       </c>
       <c r="C5" t="n">
-        <v>106.3969074477481</v>
+        <v>236.6748278012999</v>
       </c>
       <c r="D5" t="n">
-        <v>111.1829275059513</v>
+        <v>123.4302301164303</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.10580173900973</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="C6" t="n">
-        <v>174.2896699349363</v>
+        <v>315.5327303972207</v>
       </c>
       <c r="D6" t="n">
-        <v>62.14855666964009</v>
+        <v>62.9938414429966</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.8235317596096</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>180.8575620763474</v>
+        <v>281.2874069776834</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>129.6790542539612</v>
+        <v>180.7495698288803</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>64.89843198923538</v>
+        <v>70.55624400880974</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>22.56448923440869</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.23525959612074</v>
+        <v>1.629701189049705</v>
       </c>
       <c r="C2" t="n">
-        <v>2.80092620021615</v>
+        <v>4.35208757292611</v>
       </c>
       <c r="D2" t="n">
-        <v>10.43990508696058</v>
+        <v>10.61072918749953</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8389776809703</v>
+        <v>10.21508486268806</v>
       </c>
       <c r="C3" t="n">
-        <v>17.64200624531518</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="D3" t="n">
-        <v>56.7253823513807</v>
+        <v>62.21826075664161</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.36391926976863</v>
+        <v>29.68608708101505</v>
       </c>
       <c r="C4" t="n">
-        <v>55.65822259686442</v>
+        <v>91.31726271051707</v>
       </c>
       <c r="D4" t="n">
-        <v>122.8539442140374</v>
+        <v>142.3809060515064</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>93.38875036647785</v>
+        <v>47.32023934469627</v>
       </c>
       <c r="C5" t="n">
-        <v>109.5630437939441</v>
+        <v>231.0052348092745</v>
       </c>
       <c r="D5" t="n">
-        <v>125.0501138284375</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.39513957432206</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>181.5752196481519</v>
+        <v>349.2233663638585</v>
       </c>
       <c r="D6" t="n">
-        <v>74.14355012012763</v>
+        <v>74.18380177600174</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6934967032137</v>
+        <v>338.2395730487451</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>164.3102045212674</v>
+        <v>230.9855998551895</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20624310447914</v>
+        <v>74.66093116026566</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>34.59188035913637</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.354272052512856</v>
+        <v>2.328705554473434</v>
       </c>
       <c r="C2" t="n">
-        <v>5.14632146566178</v>
+        <v>8.889725461954868</v>
       </c>
       <c r="D2" t="n">
-        <v>19.36595521397258</v>
+        <v>16.03488525346315</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12306262039612</v>
+        <v>8.020878743696441</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29424657383356</v>
+        <v>22.27585540936013</v>
       </c>
       <c r="D3" t="n">
-        <v>52.42041866825843</v>
+        <v>57.30461349688632</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.18301565027996</v>
+        <v>25.14255870576081</v>
       </c>
       <c r="C4" t="n">
-        <v>49.97881212779662</v>
+        <v>79.63937376850126</v>
       </c>
       <c r="D4" t="n">
-        <v>122.892232374503</v>
+        <v>140.6579388305533</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>92.33337158441253</v>
+        <v>46.11759840699392</v>
       </c>
       <c r="C5" t="n">
-        <v>106.1514705216864</v>
+        <v>204.9152895689155</v>
       </c>
       <c r="D5" t="n">
-        <v>136.0456881160018</v>
+        <v>149.2992821233337</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>100.6291396852981</v>
+        <v>49.67054334866313</v>
       </c>
       <c r="C6" t="n">
-        <v>179.0796169839565</v>
+        <v>357.2334458828082</v>
       </c>
       <c r="D6" t="n">
-        <v>92.01528532823657</v>
+        <v>92.17629195173305</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.21545438224911</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="C7" t="n">
-        <v>239.4865532262627</v>
+        <v>405.3724628128462</v>
       </c>
       <c r="D7" t="n">
-        <v>53.65840252331367</v>
+        <v>49.82565948593412</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>215.7145143156304</v>
+        <v>308.5927558758999</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>131.6828013183289</v>
+        <v>145.8828001125547</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>58.36490101747288</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>25.23287949455151</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.398851609831464</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C2" t="n">
-        <v>6.282203559475339</v>
+        <v>13.50983015814036</v>
       </c>
       <c r="D2" t="n">
-        <v>8.911323911448298</v>
+        <v>11.01422749394497</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.093307089632453</v>
+        <v>1.719040230136165</v>
       </c>
       <c r="C2" t="n">
-        <v>2.798962704807656</v>
+        <v>5.263149442467151</v>
       </c>
       <c r="D2" t="n">
-        <v>14.0978970329842</v>
+        <v>11.92921635430299</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.14746744428205</v>
+        <v>10.87285582453342</v>
       </c>
       <c r="C3" t="n">
-        <v>18.38813450054276</v>
+        <v>29.50642725113789</v>
       </c>
       <c r="D3" t="n">
-        <v>60.01423716060751</v>
+        <v>63.65652114336319</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69.91418101023234</v>
+        <v>35.00814138573701</v>
       </c>
       <c r="C4" t="n">
-        <v>68.3316037109865</v>
+        <v>115.1707866806018</v>
       </c>
       <c r="D4" t="n">
-        <v>126.5168448985822</v>
+        <v>143.6061271864064</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.80101798233672</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="C5" t="n">
-        <v>154.7479818819035</v>
+        <v>305.0290117094841</v>
       </c>
       <c r="D5" t="n">
-        <v>127.5044830890545</v>
+        <v>134.1312800927205</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>15.37613254391355</v>
       </c>
       <c r="C6" t="n">
-        <v>198.0783985565407</v>
+        <v>326.5214324508552</v>
       </c>
       <c r="D6" t="n">
-        <v>76.35739119320418</v>
+        <v>73.13725872327464</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>151.6927830262874</v>
+        <v>217.0290744916169</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.420008090968388</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>97.05066930331843</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>25.78560345204247</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>20.63437324785945</v>
+        <v>19.74687332322034</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>20.35653864755762</v>
       </c>
       <c r="D10" t="n">
-        <v>19.78712497909446</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.59193711239859</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.823547455142832</v>
+        <v>6.393141050055229</v>
       </c>
       <c r="C2" t="n">
-        <v>5.320090809313465</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="D2" t="n">
-        <v>11.49626561673015</v>
+        <v>15.22690689286803</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>12.46819584393449</v>
       </c>
       <c r="C3" t="n">
-        <v>15.83068173097982</v>
+        <v>34.04210164475816</v>
       </c>
       <c r="D3" t="n">
-        <v>10.62251015995049</v>
+        <v>12.38965602759475</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3979517381033</v>
+        <v>13.39678620775144</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14221792301139</v>
+        <v>70.13611602881635</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576229616247447</v>
+        <v>1.576092495029581</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.078580874068749</v>
+        <v>4.648575379608647</v>
       </c>
       <c r="C2" t="n">
-        <v>3.93975353714245</v>
+        <v>10.56262354999143</v>
       </c>
       <c r="D2" t="n">
-        <v>14.92256510455152</v>
+        <v>21.62986541996573</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39995653072273</v>
+        <v>18.24578108342697</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90355204527233</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="D3" t="n">
-        <v>17.71072858461246</v>
+        <v>22.18258937745668</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.56074217004095</v>
+        <v>14.52397553662731</v>
       </c>
       <c r="C4" t="n">
-        <v>24.6703380600181</v>
+        <v>52.41649167744146</v>
       </c>
       <c r="D4" t="n">
-        <v>20.6373184909722</v>
+        <v>21.56899706230242</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44107511815202</v>
+        <v>15.436448508589</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14494539600602</v>
+        <v>86.1191337847597</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250752656453058</v>
+        <v>3.249778633387158</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.35288939418111</v>
+        <v>4.191080949429634</v>
       </c>
       <c r="C2" t="n">
-        <v>2.873575530330414</v>
+        <v>7.179520961156924</v>
       </c>
       <c r="D2" t="n">
-        <v>16.23025304660827</v>
+        <v>30.28298968519711</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.12091919853838</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C3" t="n">
-        <v>16.73388961888688</v>
+        <v>35.78470381979624</v>
       </c>
       <c r="D3" t="n">
-        <v>25.53525778745954</v>
+        <v>34.33662595603219</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.49763257952867</v>
+        <v>25.94661007553895</v>
       </c>
       <c r="C4" t="n">
-        <v>38.02014334236623</v>
+        <v>62.63943052176349</v>
       </c>
       <c r="D4" t="n">
-        <v>24.88730430265664</v>
+        <v>27.83549265850982</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.69600236904876</v>
+        <v>12.73817646260237</v>
       </c>
       <c r="C5" t="n">
-        <v>28.29887757491431</v>
+        <v>56.57321145722246</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86967390170921</v>
+        <v>30.704159450319</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73565983977362</v>
+        <v>16.72237163406062</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0875250226191</v>
+        <v>102.0064669677698</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020697951932084</v>
+        <v>4.180592908515155</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.660978246865362</v>
+        <v>5.017712516405448</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108033305196154</v>
+        <v>12.98950387488955</v>
       </c>
       <c r="D2" t="n">
-        <v>18.75334464652257</v>
+        <v>28.34796496012665</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.02903582496668</v>
+        <v>15.53615741970577</v>
       </c>
       <c r="C3" t="n">
-        <v>13.50393967191488</v>
+        <v>31.25393816469721</v>
       </c>
       <c r="D3" t="n">
-        <v>32.18659848373168</v>
+        <v>49.71079500453725</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.11399021134642</v>
+        <v>29.69884980117026</v>
       </c>
       <c r="C4" t="n">
-        <v>39.80692416409542</v>
+        <v>77.38037230102935</v>
       </c>
       <c r="D4" t="n">
-        <v>31.46010518258904</v>
+        <v>38.18605870438394</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.5820628820939</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="C5" t="n">
-        <v>51.36994862471437</v>
+        <v>87.89096322269572</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22586839190156</v>
+        <v>33.69848994827177</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>29.42396044398116</v>
+        <v>51.40136455125026</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06457019722036</v>
+        <v>18.03419974452898</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8498150961518</v>
+        <v>117.6516840476415</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881741027512516</v>
+        <v>6.011399914842994</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.03247978969815</v>
+        <v>6.484443586550183</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71024555852695</v>
+        <v>11.17719761284994</v>
       </c>
       <c r="D2" t="n">
-        <v>17.85013675861551</v>
+        <v>33.03090150938394</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.25760311360694</v>
+        <v>14.56422719250143</v>
       </c>
       <c r="C3" t="n">
-        <v>16.18411090450867</v>
+        <v>39.21100330761761</v>
       </c>
       <c r="D3" t="n">
-        <v>36.95298358784994</v>
+        <v>55.94980166502572</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.67783218875358</v>
+        <v>21.67109882354409</v>
       </c>
       <c r="C4" t="n">
-        <v>30.47737573063798</v>
+        <v>64.32410958225103</v>
       </c>
       <c r="D4" t="n">
-        <v>34.65078522139117</v>
+        <v>45.66501271533614</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.7343726449724</v>
+        <v>21.13211933391259</v>
       </c>
       <c r="C5" t="n">
-        <v>47.22206457427158</v>
+        <v>86.71286597759953</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>32.00497515844602</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.06670209062656</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="C6" t="n">
-        <v>38.23907308041327</v>
+        <v>64.48315271033901</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>20.66088043587412</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>21.63281066307846</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062302980628489</v>
+        <v>7.041362640007041</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20909044339209</v>
+        <v>66.01277475006601</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296727235471367</v>
+        <v>4.400851650004401</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.101962892521426</v>
+        <v>5.107051557491907</v>
       </c>
       <c r="C2" t="n">
-        <v>4.432590884674349</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93081999681299</v>
+        <v>23.8083635756894</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.78269926665874</v>
+        <v>19.30606860401353</v>
       </c>
       <c r="C3" t="n">
-        <v>22.76672926148353</v>
+        <v>41.95007940246621</v>
       </c>
       <c r="D3" t="n">
-        <v>43.37361357362408</v>
+        <v>70.17532589956201</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.53890704083604</v>
+        <v>25.8700337546077</v>
       </c>
       <c r="C4" t="n">
-        <v>36.96083756948391</v>
+        <v>85.01247895384405</v>
       </c>
       <c r="D4" t="n">
-        <v>46.55840312620073</v>
+        <v>64.38792318302706</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.23278168356029</v>
+        <v>27.53802310412304</v>
       </c>
       <c r="C5" t="n">
-        <v>52.54804586981054</v>
+        <v>105.8569462104124</v>
       </c>
       <c r="D5" t="n">
-        <v>36.07922813107029</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>60.6994970581718</v>
+        <v>105.6203450136889</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>41.56130731158447</v>
+        <v>66.35436383463342</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>24.20008090968387</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.00617789032851</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288966252849381</v>
+        <v>7.254298329391536</v>
       </c>
       <c r="C21" t="n">
-        <v>76.5341456549185</v>
+        <v>75.26334516743719</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377845471243208</v>
+        <v>5.440723747043652</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.649377200863646</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C2" t="n">
-        <v>3.059125846433061</v>
+        <v>4.846888415866503</v>
       </c>
       <c r="D2" t="n">
-        <v>22.31905230834699</v>
+        <v>20.49005633533518</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.3171298706675</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C3" t="n">
-        <v>19.37969968183204</v>
+        <v>31.24412068765474</v>
       </c>
       <c r="D3" t="n">
-        <v>46.05378480621788</v>
+        <v>72.65914759130644</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.26784686347268</v>
+        <v>32.21310567174634</v>
       </c>
       <c r="C4" t="n">
-        <v>48.63872651149973</v>
+        <v>96.16709636949631</v>
       </c>
       <c r="D4" t="n">
-        <v>57.40671525812799</v>
+        <v>83.96593590111695</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.97095814616266</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>61.94828013797375</v>
+        <v>132.5113963807133</v>
       </c>
       <c r="D5" t="n">
-        <v>45.23402547317179</v>
+        <v>54.24156065963628</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>29.86672865859647</v>
       </c>
       <c r="C6" t="n">
-        <v>73.90204018488291</v>
+        <v>139.0292193892078</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>67.79164247365075</v>
+        <v>111.6885275736384</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>41.64082887562846</v>
+        <v>60.24985660962675</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5124976638126</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.504565524358784</v>
+        <v>7.452277281557144</v>
       </c>
       <c r="C21" t="n">
-        <v>86.30250353012602</v>
+        <v>83.83811941751787</v>
       </c>
       <c r="D21" t="n">
-        <v>7.504565524358784</v>
+        <v>6.520742621362501</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497621036603</v>
+        <v>10.84497629862758</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907151732935</v>
+        <v>37.7890718248747</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.931318718431728</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C2" t="n">
-        <v>11.02699021410017</v>
+        <v>3.414518515370407</v>
       </c>
       <c r="D2" t="n">
-        <v>20.25443688631594</v>
+        <v>30.05816946092459</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13993225781756</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58296251434013</v>
+        <v>11.94296082216245</v>
       </c>
       <c r="D3" t="n">
-        <v>71.82466204269666</v>
+        <v>90.66440048719295</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.62976760897449</v>
+        <v>48.48557386963722</v>
       </c>
       <c r="C4" t="n">
-        <v>85.93139480501907</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="D4" t="n">
-        <v>97.72414822843174</v>
+        <v>103.1738297347058</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.10439371848221</v>
+        <v>59.17484287347651</v>
       </c>
       <c r="C5" t="n">
-        <v>154.8952440375405</v>
+        <v>73.31200981463057</v>
       </c>
       <c r="D5" t="n">
-        <v>70.0722423906161</v>
+        <v>69.23775684200632</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>54.54099370943156</v>
       </c>
       <c r="C6" t="n">
-        <v>172.3173387971044</v>
+        <v>105.8618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>45.92713935237005</v>
+        <v>45.48437113775474</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>37.06981156465531</v>
       </c>
       <c r="C7" t="n">
-        <v>155.4656394537079</v>
+        <v>120.3720860177014</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>91.04237335332795</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>49.14530832689106</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.634447478779168</v>
+        <v>7.660469115024305</v>
       </c>
       <c r="C21" t="n">
-        <v>92.56767568019741</v>
+        <v>92.88318801966969</v>
       </c>
       <c r="D21" t="n">
-        <v>7.634447478779168</v>
+        <v>7.660469115024305</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.990624491314037</v>
+        <v>10.389835954044</v>
       </c>
       <c r="C2" t="n">
-        <v>10.78548027885546</v>
+        <v>6.256678119164923</v>
       </c>
       <c r="D2" t="n">
-        <v>26.35599886820987</v>
+        <v>29.43181442561513</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.08102739556275</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="C3" t="n">
-        <v>33.23706852727577</v>
+        <v>12.53691818323177</v>
       </c>
       <c r="D3" t="n">
-        <v>70.8821842466197</v>
+        <v>92.67698328089891</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.702596865538</v>
+        <v>47.66875977970388</v>
       </c>
       <c r="C4" t="n">
-        <v>74.20245498238242</v>
+        <v>33.65529304928491</v>
       </c>
       <c r="D4" t="n">
-        <v>108.4193077184965</v>
+        <v>121.667011239603</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.64497685062371</v>
+        <v>65.65437772150545</v>
       </c>
       <c r="C5" t="n">
-        <v>154.6498071114788</v>
+        <v>71.8148445656542</v>
       </c>
       <c r="D5" t="n">
-        <v>84.23395302437635</v>
+        <v>86.29562320329464</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>65.81145735418494</v>
       </c>
       <c r="C6" t="n">
-        <v>205.243193302134</v>
+        <v>110.1285304715902</v>
       </c>
       <c r="D6" t="n">
-        <v>55.2252718592916</v>
+        <v>55.30577517103983</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.95570784678443</v>
+        <v>49.64599965605695</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4100082963978</v>
+        <v>136.6612439265645</v>
       </c>
       <c r="D7" t="n">
-        <v>41.9206269713388</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="C8" t="n">
-        <v>146.7860080004618</v>
+        <v>122.419029981056</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>13.20156137900685</v>
       </c>
       <c r="C9" t="n">
-        <v>84.7562428030356</v>
+        <v>78.65468082114168</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.800350526554685</v>
+        <v>7.837836632692932</v>
       </c>
       <c r="C21" t="n">
-        <v>100.4295130293916</v>
+        <v>100.9121466459215</v>
       </c>
       <c r="D21" t="n">
-        <v>8.775394342374021</v>
+        <v>8.817566211779548</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.861033794353459</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="C2" t="n">
-        <v>15.48707003449343</v>
+        <v>4.587707021945345</v>
       </c>
       <c r="D2" t="n">
-        <v>24.05870924027233</v>
+        <v>38.1958761814264</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.28857707178633</v>
+        <v>28.60321936323082</v>
       </c>
       <c r="C3" t="n">
-        <v>36.62409810692726</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="D3" t="n">
-        <v>73.27764864498192</v>
+        <v>93.28075811901068</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.28593492830985</v>
+        <v>45.99684343937156</v>
       </c>
       <c r="C4" t="n">
-        <v>76.869863494821</v>
+        <v>32.16205479112551</v>
       </c>
       <c r="D4" t="n">
-        <v>114.2773962697372</v>
+        <v>133.970273469224</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.28311285838414</v>
+        <v>68.32964021557801</v>
       </c>
       <c r="C5" t="n">
-        <v>145.2250291507094</v>
+        <v>66.6115817331461</v>
       </c>
       <c r="D5" t="n">
-        <v>98.37111996553043</v>
+        <v>104.9242858913779</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.99255659565609</v>
+        <v>74.94858323761002</v>
       </c>
       <c r="C6" t="n">
-        <v>222.0683854575158</v>
+        <v>112.2618682329185</v>
       </c>
       <c r="D6" t="n">
-        <v>64.32214608684252</v>
+        <v>65.61019907481435</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.02232782195297</v>
+        <v>61.44366181799087</v>
       </c>
       <c r="C7" t="n">
-        <v>234.3363047697839</v>
+        <v>146.1832149100543</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>38.97047512007713</v>
       </c>
       <c r="C8" t="n">
-        <v>190.7633964121977</v>
+        <v>147.7873906587936</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>19.52499834206056</v>
       </c>
       <c r="C9" t="n">
-        <v>122.8078020719377</v>
+        <v>110.7156155987298</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>66.62139921018856</v>
+        <v>63.9166842849886</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>40.33706792438868</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.949827979551473</v>
+        <v>8.001139703116557</v>
       </c>
       <c r="C21" t="n">
-        <v>107.3226777239449</v>
+        <v>109.0155284549631</v>
       </c>
       <c r="D21" t="n">
-        <v>9.93728497443934</v>
+        <v>10.0014246288957</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.519385593275567</v>
+        <v>11.02993545721291</v>
       </c>
       <c r="C2" t="n">
-        <v>10.90230825566083</v>
+        <v>3.119012456392117</v>
       </c>
       <c r="D2" t="n">
-        <v>20.09048501970673</v>
+        <v>31.2725913710779</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.52834449580081</v>
+        <v>33.34996951326415</v>
       </c>
       <c r="C3" t="n">
-        <v>55.64545987670921</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>80.04679906576369</v>
+        <v>101.7925107148305</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.74767514447534</v>
+        <v>32.82571623919635</v>
       </c>
       <c r="C4" t="n">
-        <v>112.3374628061455</v>
+        <v>51.15298238207581</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3509862898267</v>
+        <v>125.1639965621301</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>42.21515128261285</v>
       </c>
       <c r="C5" t="n">
-        <v>132.6832022289564</v>
+        <v>67.07791189266334</v>
       </c>
       <c r="D5" t="n">
-        <v>63.91177554646737</v>
+        <v>67.39697989654354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.43904651244335</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="C6" t="n">
-        <v>154.3248486213731</v>
+        <v>96.2819608508932</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>30.75226508782709</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>134.1460063082842</v>
+        <v>103.9032682789612</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>81.61268665403733</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>50.80937068558941</v>
+        <v>48.8124958551514</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.427281235525615</v>
+        <v>6.576727870749383</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>1.663080610994097</v>
       </c>
       <c r="D2" t="n">
-        <v>15.159166301275</v>
+        <v>21.43351587911636</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.27799883121787</v>
+        <v>36.39829613495049</v>
       </c>
       <c r="C3" t="n">
-        <v>50.21148633370311</v>
+        <v>18.91827826083604</v>
       </c>
       <c r="D3" t="n">
-        <v>78.17166095065228</v>
+        <v>103.3485808260617</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.81822211046087</v>
+        <v>46.08618248045802</v>
       </c>
       <c r="C4" t="n">
-        <v>128.584405563726</v>
+        <v>57.81512230309466</v>
       </c>
       <c r="D4" t="n">
-        <v>122.343435407829</v>
+        <v>145.1887044856523</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.34229545807943</v>
+        <v>47.36932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>167.0198281849886</v>
+        <v>81.80412745636549</v>
       </c>
       <c r="D5" t="n">
-        <v>80.03698158872123</v>
+        <v>88.25911861178827</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.58496706747763</v>
+        <v>45.32336451425826</v>
       </c>
       <c r="C6" t="n">
-        <v>184.4330872152143</v>
+        <v>105.9423582606818</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="C7" t="n">
-        <v>167.9819409351505</v>
+        <v>123.7856227853676</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>118.9141906768949</v>
+        <v>104.1437964665016</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>53.13905798776709</v>
+        <v>54.35937038414588</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.304562772494764</v>
+        <v>6.689628856737766</v>
       </c>
       <c r="C2" t="n">
-        <v>7.115707360380882</v>
+        <v>6.774059159302992</v>
       </c>
       <c r="D2" t="n">
-        <v>14.87740471015616</v>
+        <v>19.61139214003428</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.02212253330795</v>
+        <v>29.29535149472482</v>
       </c>
       <c r="C3" t="n">
-        <v>34.64096774434871</v>
+        <v>12.17367153266045</v>
       </c>
       <c r="D3" t="n">
-        <v>73.34146224575797</v>
+        <v>97.77716260446108</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.97886888105885</v>
+        <v>57.81512230309466</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0611340373625</v>
+        <v>52.30162719604458</v>
       </c>
       <c r="D4" t="n">
-        <v>131.0476105536812</v>
+        <v>159.5340019401067</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.57010198319369</v>
+        <v>57.45678439104459</v>
       </c>
       <c r="C5" t="n">
-        <v>198.9757159582223</v>
+        <v>94.98409038587891</v>
       </c>
       <c r="D5" t="n">
-        <v>99.18106182153404</v>
+        <v>116.7298020349458</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>53.89696721544566</v>
       </c>
       <c r="C6" t="n">
-        <v>220.4985708784251</v>
+        <v>117.6153384641764</v>
       </c>
       <c r="D6" t="n">
-        <v>50.31456984264904</v>
+        <v>54.6214970211798</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.59532432386784</v>
+        <v>36.47094546506476</v>
       </c>
       <c r="C7" t="n">
-        <v>213.3161046741554</v>
+        <v>139.8352342543944</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>16.68971097219578</v>
       </c>
       <c r="C8" t="n">
-        <v>163.9764103018235</v>
+        <v>133.1838935581223</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>90.63592980376974</v>
+        <v>86.97499261463339</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.999820073550753</v>
+        <v>3.951534509593412</v>
       </c>
       <c r="C2" t="n">
-        <v>3.503857556456866</v>
+        <v>3.11508546557513</v>
       </c>
       <c r="D2" t="n">
-        <v>10.50764567855361</v>
+        <v>13.54811831860598</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.71778074499143</v>
+        <v>29.24135537099124</v>
       </c>
       <c r="C3" t="n">
-        <v>34.04210164475816</v>
+        <v>19.24716374175872</v>
       </c>
       <c r="D3" t="n">
-        <v>71.91301933607886</v>
+        <v>95.4602380224386</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.86324363613598</v>
+        <v>64.23477054116456</v>
       </c>
       <c r="C4" t="n">
-        <v>126.3764549768749</v>
+        <v>49.28962523941536</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9222088894449</v>
+        <v>171.428857124761</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.77274292089604</v>
+        <v>59.69026041820608</v>
       </c>
       <c r="C5" t="n">
-        <v>240.7245370813179</v>
+        <v>109.8084807200058</v>
       </c>
       <c r="D5" t="n">
-        <v>101.7336058525757</v>
+        <v>127.430852011236</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>45.04160292313942</v>
       </c>
       <c r="C6" t="n">
-        <v>257.3690876591183</v>
+        <v>149.6556565399753</v>
       </c>
       <c r="D6" t="n">
-        <v>48.90576188705487</v>
+        <v>53.13218575383738</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>217.7477138111255</v>
+        <v>158.2204235118244</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>113.4065860560703</v>
+        <v>105.8127675637212</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.370920705756047</v>
+        <v>5.528221322613789</v>
       </c>
       <c r="C2" t="n">
-        <v>7.486807992586176</v>
+        <v>4.657411108946868</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59760661444582</v>
+        <v>12.25712008752143</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.55517047898496</v>
+        <v>21.58372327786613</v>
       </c>
       <c r="C3" t="n">
-        <v>24.04791001552562</v>
+        <v>15.53124868118454</v>
       </c>
       <c r="D3" t="n">
-        <v>64.71189992542851</v>
+        <v>85.27460559087795</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04268248183489</v>
+        <v>60.38042905429158</v>
       </c>
       <c r="C4" t="n">
-        <v>107.8705107518225</v>
+        <v>49.09818443708723</v>
       </c>
       <c r="D4" t="n">
-        <v>142.0746007677814</v>
+        <v>178.7418957736955</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.39953992456201</v>
+        <v>75.88909753827845</v>
       </c>
       <c r="C5" t="n">
-        <v>236.6748278012999</v>
+        <v>101.6354310821511</v>
       </c>
       <c r="D5" t="n">
-        <v>123.4302301164303</v>
+        <v>154.6007197262665</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.70951015719674</v>
+        <v>59.81396062894117</v>
       </c>
       <c r="C6" t="n">
-        <v>315.5327303972207</v>
+        <v>162.8581996666864</v>
       </c>
       <c r="D6" t="n">
-        <v>62.9938414429966</v>
+        <v>75.39135145222532</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>281.2874069776834</v>
+        <v>187.7445222216388</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>180.7495698288803</v>
+        <v>150.5411929692059</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>71.77655640518853</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.629701189049705</v>
+        <v>3.911282853719293</v>
       </c>
       <c r="C2" t="n">
-        <v>4.35208757292611</v>
+        <v>3.276092089071606</v>
       </c>
       <c r="D2" t="n">
-        <v>10.61072918749953</v>
+        <v>9.399252520458962</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.21508486268806</v>
+        <v>20.6854241284803</v>
       </c>
       <c r="C3" t="n">
-        <v>26.42864819832414</v>
+        <v>17.10204500797944</v>
       </c>
       <c r="D3" t="n">
-        <v>62.21826075664161</v>
+        <v>78.24529202847079</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.68608708101505</v>
+        <v>54.39471330149878</v>
       </c>
       <c r="C4" t="n">
-        <v>91.31726271051707</v>
+        <v>45.80540263704343</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3809060515064</v>
+        <v>180.7966937186841</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.32023934469627</v>
+        <v>84.03760348352698</v>
       </c>
       <c r="C5" t="n">
-        <v>231.0052348092745</v>
+        <v>99.74556675147596</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>174.6529165855076</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>71.32593420893927</v>
       </c>
       <c r="C6" t="n">
-        <v>349.2233663638585</v>
+        <v>170.9085308415103</v>
       </c>
       <c r="D6" t="n">
-        <v>74.18380177600174</v>
+        <v>91.33100717837654</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>338.2395730487451</v>
+        <v>214.9330431430499</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>45.57371017884118</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>230.9855998551895</v>
+        <v>186.3406230045658</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>74.66093116026566</v>
+        <v>84.97811778419538</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.328705554473434</v>
+        <v>6.632687489891451</v>
       </c>
       <c r="C2" t="n">
-        <v>8.889725461954868</v>
+        <v>6.060328578315561</v>
       </c>
       <c r="D2" t="n">
-        <v>16.03488525346315</v>
+        <v>10.7864620265597</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.020878743696441</v>
+        <v>17.02841393016093</v>
       </c>
       <c r="C3" t="n">
-        <v>22.27585540936013</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="D3" t="n">
-        <v>57.30461349688632</v>
+        <v>69.11012964045422</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.14255870576081</v>
+        <v>47.52836985799659</v>
       </c>
       <c r="C4" t="n">
-        <v>79.63937376850126</v>
+        <v>44.24835077810799</v>
       </c>
       <c r="D4" t="n">
-        <v>140.6579388305533</v>
+        <v>178.7674212140059</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.11759840699392</v>
+        <v>83.20311793491719</v>
       </c>
       <c r="C5" t="n">
-        <v>204.9152895689155</v>
+        <v>92.72607066611126</v>
       </c>
       <c r="D5" t="n">
-        <v>149.2992821233337</v>
+        <v>194.2387832852315</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.67054334866313</v>
+        <v>88.15112636432112</v>
       </c>
       <c r="C6" t="n">
-        <v>357.2334458828082</v>
+        <v>166.440597039483</v>
       </c>
       <c r="D6" t="n">
-        <v>92.17629195173305</v>
+        <v>116.3272854762046</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>45.8132566186774</v>
       </c>
       <c r="C7" t="n">
-        <v>405.3724628128462</v>
+        <v>230.2640152925681</v>
       </c>
       <c r="D7" t="n">
-        <v>49.82565948593412</v>
+        <v>56.59284641130738</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>308.5927558758999</v>
+        <v>230.1511143065797</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>145.8828001125547</v>
+        <v>141.5562379799391</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>57.65313393189394</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.868887775987432</v>
+        <v>8.217228284545802</v>
       </c>
       <c r="C2" t="n">
-        <v>13.50983015814036</v>
+        <v>10.82965892554656</v>
       </c>
       <c r="D2" t="n">
-        <v>11.01422749394497</v>
+        <v>10.18661417926491</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.719040230136165</v>
+        <v>4.643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>5.263149442467151</v>
+        <v>3.344814428368883</v>
       </c>
       <c r="D2" t="n">
-        <v>11.92921635430299</v>
+        <v>7.939393684243956</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.87285582453342</v>
+        <v>23.56194490192345</v>
       </c>
       <c r="C3" t="n">
-        <v>29.50642725113789</v>
+        <v>20.05710559776234</v>
       </c>
       <c r="D3" t="n">
-        <v>63.65652114336319</v>
+        <v>73.75379628154163</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.00814138573701</v>
+        <v>63.89017709697393</v>
       </c>
       <c r="C4" t="n">
-        <v>115.1707866806018</v>
+        <v>61.23553130469055</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6061271864064</v>
+        <v>184.587221604781</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.9798095710341</v>
+        <v>53.50524988145118</v>
       </c>
       <c r="C5" t="n">
-        <v>305.0290117094841</v>
+        <v>139.8745041625643</v>
       </c>
       <c r="D5" t="n">
-        <v>134.1312800927205</v>
+        <v>175.7573827527852</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.37613254391355</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>326.5214324508552</v>
+        <v>187.5324647175215</v>
       </c>
       <c r="D6" t="n">
-        <v>73.13725872327464</v>
+        <v>90.16370915802707</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.551382356888213</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>217.0290744916169</v>
+        <v>161.8136201093678</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>104.3106935762236</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.393141050055229</v>
+        <v>8.332092765942679</v>
       </c>
       <c r="C2" t="n">
-        <v>6.243915399009714</v>
+        <v>7.301257676483528</v>
       </c>
       <c r="D2" t="n">
-        <v>15.22690689286803</v>
+        <v>11.38336463074177</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.46819584393449</v>
+        <v>17.44565670446582</v>
       </c>
       <c r="C3" t="n">
-        <v>34.04210164475816</v>
+        <v>27.2876774395401</v>
       </c>
       <c r="D3" t="n">
-        <v>12.38965602759475</v>
+        <v>11.69261515757951</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39678620775144</v>
+        <v>13.39698468219892</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13611602881635</v>
+        <v>70.13715510092375</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576092495029581</v>
+        <v>1.576115844964579</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.648575379608647</v>
+        <v>6.557092916664446</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56262354999143</v>
+        <v>4.16751900452771</v>
       </c>
       <c r="D2" t="n">
-        <v>21.62986541996573</v>
+        <v>21.97347711645211</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24578108342697</v>
+        <v>24.27862072602362</v>
       </c>
       <c r="C3" t="n">
-        <v>27.9798095710341</v>
+        <v>28.02889695624643</v>
       </c>
       <c r="D3" t="n">
-        <v>22.18258937745668</v>
+        <v>18.42740440871263</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.52397553662731</v>
+        <v>20.13957240491907</v>
       </c>
       <c r="C4" t="n">
-        <v>52.41649167744146</v>
+        <v>42.12973923234337</v>
       </c>
       <c r="D4" t="n">
-        <v>21.56899706230242</v>
+        <v>21.19887817780138</v>
       </c>
     </row>
     <row r="5">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.3139636433765</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.436448508589</v>
+        <v>15.43723101043667</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1191337847597</v>
+        <v>86.12349932138352</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249778633387158</v>
+        <v>3.249943370618246</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.191080949429634</v>
+        <v>6.35288939418111</v>
       </c>
       <c r="C2" t="n">
-        <v>7.179520961156924</v>
+        <v>3.382120841130261</v>
       </c>
       <c r="D2" t="n">
-        <v>30.28298968519711</v>
+        <v>25.37621465937156</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00877897607599</v>
+        <v>23.60612354861455</v>
       </c>
       <c r="C3" t="n">
-        <v>35.78470381979624</v>
+        <v>20.96522222419064</v>
       </c>
       <c r="D3" t="n">
-        <v>34.33662595603219</v>
+        <v>31.73008580125691</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.94661007553895</v>
+        <v>34.90603962449534</v>
       </c>
       <c r="C4" t="n">
-        <v>62.63943052176349</v>
+        <v>58.36391926976863</v>
       </c>
       <c r="D4" t="n">
-        <v>27.83549265850982</v>
+        <v>25.67859295227957</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.73817646260237</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>56.57321145722246</v>
+        <v>45.92124886614456</v>
       </c>
       <c r="D5" t="n">
-        <v>30.704159450319</v>
+        <v>30.2869166760141</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5221,7 +5221,7 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72237163406062</v>
+        <v>16.72446223347498</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0064669677698</v>
+        <v>102.0192196241973</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180592908515155</v>
+        <v>4.181115558368744</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.017712516405448</v>
+        <v>7.969827863075607</v>
       </c>
       <c r="C2" t="n">
-        <v>12.98950387488955</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="D2" t="n">
-        <v>28.34796496012665</v>
+        <v>32.00399341074177</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.53615741970577</v>
+        <v>22.545836028028</v>
       </c>
       <c r="C3" t="n">
-        <v>31.25393816469721</v>
+        <v>16.49336143134641</v>
       </c>
       <c r="D3" t="n">
-        <v>49.71079500453725</v>
+        <v>43.95775345765094</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.69884980117026</v>
+        <v>40.70031457496002</v>
       </c>
       <c r="C4" t="n">
-        <v>77.38037230102935</v>
+        <v>55.10942563019046</v>
       </c>
       <c r="D4" t="n">
-        <v>38.18605870438394</v>
+        <v>35.25063306868597</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.40272184738622</v>
+        <v>34.14027641518284</v>
       </c>
       <c r="C5" t="n">
-        <v>87.89096322269572</v>
+        <v>78.2452920284708</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69848994827177</v>
+        <v>32.37313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>14.24908617943821</v>
       </c>
       <c r="C6" t="n">
-        <v>51.40136455125026</v>
+        <v>43.59254331167113</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03419974452898</v>
+        <v>18.040440980952</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6516840476415</v>
+        <v>117.6924006852583</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011399914842994</v>
+        <v>6.013480326983999</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.484443586550183</v>
+        <v>8.718901361415924</v>
       </c>
       <c r="C2" t="n">
-        <v>11.17719761284994</v>
+        <v>4.446335352533804</v>
       </c>
       <c r="D2" t="n">
-        <v>33.03090150938394</v>
+        <v>35.66591234758238</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.56422719250143</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="C3" t="n">
-        <v>39.21100330761761</v>
+        <v>15.4674350804085</v>
       </c>
       <c r="D3" t="n">
-        <v>55.94980166502572</v>
+        <v>55.03677630007619</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.67109882354409</v>
+        <v>30.45185029032756</v>
       </c>
       <c r="C4" t="n">
-        <v>64.32410958225103</v>
+        <v>39.65377152223292</v>
       </c>
       <c r="D4" t="n">
-        <v>45.66501271533614</v>
+        <v>42.41051907575796</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.13211933391259</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C5" t="n">
-        <v>86.71286597759953</v>
+        <v>66.73430019617695</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>30.11511082777092</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.31700669748049</v>
+        <v>16.18116566139593</v>
       </c>
       <c r="C6" t="n">
-        <v>64.48315271033901</v>
+        <v>57.51961624411638</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>30.42239785920016</v>
+        <v>26.64954143177966</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
         <v>29.37389131106456</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5913,10 +5913,10 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.041362640007041</v>
+        <v>7.046340621979251</v>
       </c>
       <c r="C21" t="n">
-        <v>66.01277475006601</v>
+        <v>66.05944333105548</v>
       </c>
       <c r="D21" t="n">
-        <v>4.400851650004401</v>
+        <v>4.403962888737031</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.107051557491907</v>
+        <v>7.577128781376882</v>
       </c>
       <c r="C2" t="n">
-        <v>6.037748381117884</v>
+        <v>3.439062207976577</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8083635756894</v>
+        <v>35.26732277965817</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30606860401353</v>
+        <v>27.25331626989146</v>
       </c>
       <c r="C3" t="n">
-        <v>41.95007940246621</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="D3" t="n">
-        <v>70.17532589956201</v>
+        <v>71.69703484114456</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.8700337546077</v>
+        <v>38.65827935012666</v>
       </c>
       <c r="C4" t="n">
-        <v>85.01247895384405</v>
+        <v>39.15602543617979</v>
       </c>
       <c r="D4" t="n">
-        <v>64.38792318302706</v>
+        <v>61.41420938686347</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.53802310412304</v>
+        <v>38.68085954732433</v>
       </c>
       <c r="C5" t="n">
-        <v>105.8569462104124</v>
+        <v>70.17041716104079</v>
       </c>
       <c r="D5" t="n">
-        <v>41.72427743048944</v>
+        <v>38.77903431774902</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.49438423677967</v>
+        <v>29.58496706747763</v>
       </c>
       <c r="C6" t="n">
-        <v>105.6203450136889</v>
+        <v>86.2190468823634</v>
       </c>
       <c r="D6" t="n">
-        <v>33.6906359666378</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>66.35436383463342</v>
+        <v>59.5272902993011</v>
       </c>
       <c r="D7" t="n">
         <v>33.35684174719388</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6224,7 +6224,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.254298329391536</v>
+        <v>7.264350740473261</v>
       </c>
       <c r="C21" t="n">
-        <v>75.26334516743719</v>
+        <v>75.36763893241009</v>
       </c>
       <c r="D21" t="n">
-        <v>5.440723747043652</v>
+        <v>5.448263055354945</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.212679398923063</v>
+        <v>6.94390151213769</v>
       </c>
       <c r="C2" t="n">
-        <v>4.846888415866503</v>
+        <v>2.507383636646354</v>
       </c>
       <c r="D2" t="n">
-        <v>20.49005633533518</v>
+        <v>34.87462369795945</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.31450342272425</v>
+        <v>26.62008900065226</v>
       </c>
       <c r="C3" t="n">
-        <v>31.24412068765474</v>
+        <v>14.69676313257475</v>
       </c>
       <c r="D3" t="n">
-        <v>72.65914759130644</v>
+        <v>83.27674901273569</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.21310567174634</v>
+        <v>46.43077592464865</v>
       </c>
       <c r="C4" t="n">
-        <v>96.16709636949631</v>
+        <v>40.66202641449439</v>
       </c>
       <c r="D4" t="n">
-        <v>83.96593590111695</v>
+        <v>83.54476613599506</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>49.40645321622075</v>
       </c>
       <c r="C5" t="n">
-        <v>132.5113963807133</v>
+        <v>71.44668917656163</v>
       </c>
       <c r="D5" t="n">
-        <v>54.24156065963628</v>
+        <v>52.05717201768713</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.86672865859647</v>
+        <v>41.66046382971341</v>
       </c>
       <c r="C6" t="n">
-        <v>139.0292193892078</v>
+        <v>99.34108669732626</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>111.6885275736384</v>
+        <v>95.15982322493909</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>60.24985660962675</v>
+        <v>55.66018609227291</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.452277281557144</v>
+        <v>7.469346514651497</v>
       </c>
       <c r="C21" t="n">
-        <v>83.83811941751787</v>
+        <v>84.03014828982934</v>
       </c>
       <c r="D21" t="n">
-        <v>6.520742621362501</v>
+        <v>6.53567820032006</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_11_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629862758</v>
+        <v>10.84497633764327</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890718248747</v>
+        <v>37.78907196082397</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.066619975168541</v>
+        <v>1.349903093339364</v>
       </c>
       <c r="C2" t="n">
-        <v>3.414518515370407</v>
+        <v>2.183406894244906</v>
       </c>
       <c r="D2" t="n">
-        <v>30.05816946092459</v>
+        <v>10.01186308790897</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.19655482949439</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C3" t="n">
-        <v>11.94296082216245</v>
+        <v>30.09547587368597</v>
       </c>
       <c r="D3" t="n">
-        <v>90.66440048719295</v>
+        <v>52.12098561846316</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.48557386963722</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C4" t="n">
-        <v>38.17329598422873</v>
+        <v>97.32850390362029</v>
       </c>
       <c r="D4" t="n">
-        <v>103.1738297347058</v>
+        <v>66.91494177375834</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.17484287347651</v>
+        <v>14.48077863764046</v>
       </c>
       <c r="C5" t="n">
-        <v>73.31200981463057</v>
+        <v>106.6178006812036</v>
       </c>
       <c r="D5" t="n">
-        <v>69.23775684200632</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.54099370943156</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>105.8618549489336</v>
+        <v>56.59382815901164</v>
       </c>
       <c r="D6" t="n">
-        <v>45.48437113775474</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.06981156465531</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3720860177014</v>
+        <v>30.60205768907732</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>30.00319158948677</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>91.04237335332795</v>
+        <v>27.70492021384499</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>49.14530832689106</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660469115024305</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.88318801966969</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660469115024305</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.389835954044</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C2" t="n">
-        <v>6.256678119164923</v>
+        <v>5.76187727622453</v>
       </c>
       <c r="D2" t="n">
-        <v>29.43181442561513</v>
+        <v>15.40754847044944</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.25407703341745</v>
+        <v>7.706719478337462</v>
       </c>
       <c r="C3" t="n">
-        <v>12.53691818323177</v>
+        <v>16.99405276051229</v>
       </c>
       <c r="D3" t="n">
-        <v>92.67698328089891</v>
+        <v>48.03691516879643</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.66875977970388</v>
+        <v>20.43311496848886</v>
       </c>
       <c r="C4" t="n">
-        <v>33.65529304928491</v>
+        <v>85.42088599881073</v>
       </c>
       <c r="D4" t="n">
-        <v>121.667011239603</v>
+        <v>78.04403374910019</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.65437772150545</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C5" t="n">
-        <v>71.8148445656542</v>
+        <v>147.7039421039326</v>
       </c>
       <c r="D5" t="n">
-        <v>86.29562320329464</v>
+        <v>59.73934780341843</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.81145735418494</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>110.1285304715902</v>
+        <v>117.816596743547</v>
       </c>
       <c r="D6" t="n">
-        <v>55.30577517103983</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.64599965605695</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>136.6612439265645</v>
+        <v>57.97023844036566</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.45595720759379</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>122.419029981056</v>
+        <v>34.79804737702819</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.20156137900685</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>78.65468082114168</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.837836632692932</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9121466459215</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.817566211779548</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.24730261047896</v>
+        <v>1.120174130545611</v>
       </c>
       <c r="C2" t="n">
-        <v>4.587707021945345</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="D2" t="n">
-        <v>38.1958761814264</v>
+        <v>10.39278119715673</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.60321936323082</v>
+        <v>8.310494316449249</v>
       </c>
       <c r="C3" t="n">
-        <v>17.87762569433442</v>
+        <v>21.04867077905162</v>
       </c>
       <c r="D3" t="n">
-        <v>93.28075811901068</v>
+        <v>50.44219704420112</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.99684343937156</v>
+        <v>22.38581115223577</v>
       </c>
       <c r="C4" t="n">
-        <v>32.16205479112551</v>
+        <v>75.63187963976578</v>
       </c>
       <c r="D4" t="n">
-        <v>133.970273469224</v>
+        <v>84.80827543136071</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.32964021557801</v>
+        <v>20.7148765596077</v>
       </c>
       <c r="C5" t="n">
-        <v>66.6115817331461</v>
+        <v>170.6522946907018</v>
       </c>
       <c r="D5" t="n">
-        <v>104.9242858913779</v>
+        <v>67.78967897824226</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.94858323761002</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="C6" t="n">
-        <v>112.2618682329185</v>
+        <v>155.2103850506038</v>
       </c>
       <c r="D6" t="n">
-        <v>65.61019907481435</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>61.44366181799087</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>146.1832149100543</v>
+        <v>57.73069200052944</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.97047512007713</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>147.7873906587936</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.52499834206056</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>110.7156155987298</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>63.9166842849886</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001139703116557</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.0155284549631</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0014246288957</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.02993545721291</v>
+        <v>0.9130253649495336</v>
       </c>
       <c r="C2" t="n">
-        <v>3.119012456392117</v>
+        <v>4.35503281603885</v>
       </c>
       <c r="D2" t="n">
-        <v>31.2725913710779</v>
+        <v>10.15028951420777</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.34996951326415</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C3" t="n">
-        <v>24.90203051822035</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="D3" t="n">
-        <v>101.7925107148305</v>
+        <v>47.11898106532567</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.82571623919635</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="C4" t="n">
-        <v>51.15298238207581</v>
+        <v>63.34138013029996</v>
       </c>
       <c r="D4" t="n">
-        <v>125.1639965621301</v>
+        <v>90.67912670275663</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.21515128261285</v>
+        <v>27.43984833369836</v>
       </c>
       <c r="C5" t="n">
-        <v>67.07791189266334</v>
+        <v>155.6560985083318</v>
       </c>
       <c r="D5" t="n">
-        <v>67.39697989654354</v>
+        <v>82.83496254582464</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>96.2819608508932</v>
+        <v>217.6004516554886</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>49.3887817575443</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>103.9032682789612</v>
+        <v>138.5776154452543</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>81.61268665403733</v>
+        <v>56.99536297004857</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>48.8124958551514</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.576727870749383</v>
+        <v>0.5782493978013713</v>
       </c>
       <c r="C2" t="n">
-        <v>1.663080610994097</v>
+        <v>2.259001467471911</v>
       </c>
       <c r="D2" t="n">
-        <v>21.43351587911636</v>
+        <v>6.937029278207961</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>36.39829613495049</v>
+        <v>4.71238898038469</v>
       </c>
       <c r="C3" t="n">
-        <v>18.91827826083604</v>
+        <v>15.9583089325319</v>
       </c>
       <c r="D3" t="n">
-        <v>103.3485808260617</v>
+        <v>45.30274781246906</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.08618248045802</v>
+        <v>16.66811252270235</v>
       </c>
       <c r="C4" t="n">
-        <v>57.81512230309466</v>
+        <v>50.92325341928206</v>
       </c>
       <c r="D4" t="n">
-        <v>145.1887044856523</v>
+        <v>93.67836593923064</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.36932672990861</v>
+        <v>29.7960428238907</v>
       </c>
       <c r="C5" t="n">
-        <v>81.80412745636549</v>
+        <v>143.7524075943392</v>
       </c>
       <c r="D5" t="n">
-        <v>88.25911861178827</v>
+        <v>94.19869222248147</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.32336451425826</v>
+        <v>24.75476836258333</v>
       </c>
       <c r="C6" t="n">
-        <v>105.9423582606818</v>
+        <v>240.5841471596107</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>58.84792088796232</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>123.7856227853676</v>
+        <v>206.0698248691097</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>104.1437964665016</v>
+        <v>93.2120357797134</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.689628856737766</v>
+        <v>1.512873212244335</v>
       </c>
       <c r="C2" t="n">
-        <v>6.774059159302992</v>
+        <v>13.46172452063226</v>
       </c>
       <c r="D2" t="n">
-        <v>19.61139214003428</v>
+        <v>16.21258158793183</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.29535149472482</v>
+        <v>3.303581024790517</v>
       </c>
       <c r="C3" t="n">
-        <v>12.17367153266045</v>
+        <v>12.13931036301181</v>
       </c>
       <c r="D3" t="n">
-        <v>97.77716260446108</v>
+        <v>40.65417243286042</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.81512230309466</v>
+        <v>13.0052118381575</v>
       </c>
       <c r="C4" t="n">
-        <v>52.30162719604458</v>
+        <v>45.1545039091278</v>
       </c>
       <c r="D4" t="n">
-        <v>159.5340019401067</v>
+        <v>94.99292611521713</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.45678439104459</v>
+        <v>28.24979018970198</v>
       </c>
       <c r="C5" t="n">
-        <v>94.98409038587891</v>
+        <v>118.7669285212579</v>
       </c>
       <c r="D5" t="n">
-        <v>116.7298020349458</v>
+        <v>105.3415286656828</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.89696721544566</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="C6" t="n">
-        <v>117.6153384641764</v>
+        <v>238.2898027747858</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6214970211798</v>
+        <v>72.73474216453346</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.47094546506476</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8352342543944</v>
+        <v>272.9032815834156</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>47.9691745772034</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.68971097219578</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>133.1838935581223</v>
+        <v>175.7426565372215</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>42.55876297909923</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>86.97499261463339</v>
+        <v>78.87655580230145</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>34.11769621798515</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.8226478228966</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.951534509593412</v>
+        <v>1.004327901444487</v>
       </c>
       <c r="C2" t="n">
-        <v>3.11508546557513</v>
+        <v>6.783876636345459</v>
       </c>
       <c r="D2" t="n">
-        <v>13.54811831860598</v>
+        <v>11.67396195119882</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.24135537099124</v>
+        <v>5.163992924338223</v>
       </c>
       <c r="C3" t="n">
-        <v>19.24716374175872</v>
+        <v>29.35916509550086</v>
       </c>
       <c r="D3" t="n">
-        <v>95.4602380224386</v>
+        <v>46.52502370425634</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64.23477054116456</v>
+        <v>19.98641976305657</v>
       </c>
       <c r="C4" t="n">
-        <v>49.28962523941536</v>
+        <v>63.91570253728434</v>
       </c>
       <c r="D4" t="n">
-        <v>171.428857124761</v>
+        <v>100.123539617611</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.69026041820608</v>
+        <v>20.24854640009047</v>
       </c>
       <c r="C5" t="n">
-        <v>109.8084807200058</v>
+        <v>189.4527632270282</v>
       </c>
       <c r="D5" t="n">
-        <v>127.430852011236</v>
+        <v>99.72102305886979</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.04160292313942</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>149.6556565399753</v>
+        <v>242.7979882326872</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>63.91962952810134</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>158.2204235118244</v>
+        <v>123.5460763455314</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>105.8127675637212</v>
+        <v>58.0801941832413</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.56913593102267</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.528221322613789</v>
+        <v>0.5163992924338223</v>
       </c>
       <c r="C2" t="n">
-        <v>4.657411108946868</v>
+        <v>3.501894061048373</v>
       </c>
       <c r="D2" t="n">
-        <v>12.25712008752143</v>
+        <v>8.642325040484671</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.58372327786613</v>
+        <v>4.3245986372072</v>
       </c>
       <c r="C3" t="n">
-        <v>15.53124868118454</v>
+        <v>28.09271055702248</v>
       </c>
       <c r="D3" t="n">
-        <v>85.27460559087795</v>
+        <v>45.35674393620264</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.38042905429158</v>
+        <v>14.00070401026376</v>
       </c>
       <c r="C4" t="n">
-        <v>49.09818443708723</v>
+        <v>66.28956848615313</v>
       </c>
       <c r="D4" t="n">
-        <v>178.7418957736955</v>
+        <v>96.53721525399736</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>75.88909753827845</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="C5" t="n">
-        <v>101.6354310821511</v>
+        <v>139.5799798512903</v>
       </c>
       <c r="D5" t="n">
-        <v>154.6007197262665</v>
+        <v>100.8745766113598</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.81396062894117</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>162.8581996666864</v>
+        <v>226.9388358182842</v>
       </c>
       <c r="D6" t="n">
-        <v>75.39135145222532</v>
+        <v>66.65674212754145</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>187.7445222216388</v>
+        <v>164.0294246778528</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>150.5411929692059</v>
+        <v>67.34298377280996</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.911282853719293</v>
+        <v>0.5399612373357457</v>
       </c>
       <c r="C2" t="n">
-        <v>3.276092089071606</v>
+        <v>6.706318567709961</v>
       </c>
       <c r="D2" t="n">
-        <v>9.399252520458962</v>
+        <v>9.008516934168732</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.6854241284803</v>
+        <v>2.910881943091793</v>
       </c>
       <c r="C3" t="n">
-        <v>17.10204500797944</v>
+        <v>19.18825887950391</v>
       </c>
       <c r="D3" t="n">
-        <v>78.24529202847079</v>
+        <v>41.74391238457438</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.39471330149878</v>
+        <v>11.12909197534184</v>
       </c>
       <c r="C4" t="n">
-        <v>45.80540263704343</v>
+        <v>69.42919764433444</v>
       </c>
       <c r="D4" t="n">
-        <v>180.7966937186841</v>
+        <v>97.69862278812133</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84.03760348352698</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="C5" t="n">
-        <v>99.74556675147596</v>
+        <v>130.0324834274901</v>
       </c>
       <c r="D5" t="n">
-        <v>174.6529165855076</v>
+        <v>113.2691413774758</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.32593420893927</v>
+        <v>19.52205309894783</v>
       </c>
       <c r="C6" t="n">
-        <v>170.9085308415103</v>
+        <v>227.5828623122702</v>
       </c>
       <c r="D6" t="n">
-        <v>91.33100717837654</v>
+        <v>82.79765613306327</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>214.9330431430499</v>
+        <v>254.0389994463131</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>186.3406230045658</v>
+        <v>145.3673825678252</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>84.97811778419538</v>
+        <v>57.57655761096267</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.632687489891451</v>
+        <v>0.5988660995905544</v>
       </c>
       <c r="C2" t="n">
-        <v>6.060328578315561</v>
+        <v>7.888342803623122</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7864620265597</v>
+        <v>14.83518955887355</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02841393016093</v>
+        <v>2.356194490192345</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0207398749762</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="D3" t="n">
-        <v>69.11012964045422</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.52836985799659</v>
+        <v>8.206429059799088</v>
       </c>
       <c r="C4" t="n">
-        <v>44.24835077810799</v>
+        <v>57.66196966123216</v>
       </c>
       <c r="D4" t="n">
-        <v>178.7674212140059</v>
+        <v>96.70313061601506</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>83.20311793491719</v>
+        <v>19.16862392541898</v>
       </c>
       <c r="C5" t="n">
-        <v>92.72607066611126</v>
+        <v>129.0998231084556</v>
       </c>
       <c r="D5" t="n">
-        <v>194.2387832852315</v>
+        <v>122.7184630308513</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>88.15112636432112</v>
+        <v>24.03023855684918</v>
       </c>
       <c r="C6" t="n">
-        <v>166.440597039483</v>
+        <v>218.1237231818521</v>
       </c>
       <c r="D6" t="n">
-        <v>116.3272854762046</v>
+        <v>97.65051715061327</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.8132566186774</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>230.2640152925681</v>
+        <v>294.5223477786346</v>
       </c>
       <c r="D7" t="n">
-        <v>56.59284641130738</v>
+        <v>58.4493313200381</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>230.1511143065797</v>
+        <v>241.3332206579509</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>141.5562379799391</v>
+        <v>117.3718650335231</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>57.65313393189394</v>
+        <v>47.26133448244146</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.217228284545802</v>
+        <v>3.068943323475529</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82965892554656</v>
+        <v>3.796418372322416</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18661417926491</v>
+        <v>13.25261225962769</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.643666641087413</v>
+        <v>0.9061531310198059</v>
       </c>
       <c r="C2" t="n">
-        <v>3.344814428368883</v>
+        <v>18.4833640278547</v>
       </c>
       <c r="D2" t="n">
-        <v>7.939393684243956</v>
+        <v>13.48037772701295</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.56194490192345</v>
+        <v>2.164753687864217</v>
       </c>
       <c r="C3" t="n">
-        <v>20.05710559776234</v>
+        <v>26.83607349558656</v>
       </c>
       <c r="D3" t="n">
-        <v>73.75379628154163</v>
+        <v>41.40520942660923</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.89017709697393</v>
+        <v>6.330309196983433</v>
       </c>
       <c r="C4" t="n">
-        <v>61.23553130469055</v>
+        <v>57.53434245968008</v>
       </c>
       <c r="D4" t="n">
-        <v>184.587221604781</v>
+        <v>94.64833267102649</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.50524988145118</v>
+        <v>16.3460992757094</v>
       </c>
       <c r="C5" t="n">
-        <v>139.8745041625643</v>
+        <v>118.0060740504666</v>
       </c>
       <c r="D5" t="n">
-        <v>175.7573827527852</v>
+        <v>127.5044830890545</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.41766904712818</v>
+        <v>24.99627829782805</v>
       </c>
       <c r="C6" t="n">
-        <v>187.5324647175215</v>
+        <v>211.0394317480071</v>
       </c>
       <c r="D6" t="n">
-        <v>90.16370915802707</v>
+        <v>112.2216165770444</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8136201093678</v>
+        <v>307.5776287497087</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>70.00744704213579</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>104.3106935762236</v>
+        <v>312.4313893995049</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>42.05807164993335</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>197.9124831945229</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>87.68970494332511</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.91890015564179</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>20.25738212942868</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.332092765942679</v>
+        <v>3.842560514422016</v>
       </c>
       <c r="C2" t="n">
-        <v>7.301257676483528</v>
+        <v>7.644869372969912</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38336463074177</v>
+        <v>17.21985473248905</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.44565670446582</v>
+        <v>5.080544369477244</v>
       </c>
       <c r="C3" t="n">
-        <v>27.2876774395401</v>
+        <v>7.495643721924397</v>
       </c>
       <c r="D3" t="n">
-        <v>11.69261515757951</v>
+        <v>12.0509530696296</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39698468219892</v>
+        <v>11.67839954098669</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13715510092375</v>
+        <v>59.94911764373167</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576115844964579</v>
+        <v>0.7785599693991125</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.557092916664446</v>
+        <v>2.756747553525043</v>
       </c>
       <c r="C2" t="n">
-        <v>4.16751900452771</v>
+        <v>7.384706231344508</v>
       </c>
       <c r="D2" t="n">
-        <v>21.97347711645211</v>
+        <v>13.5422278323805</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.27862072602362</v>
+        <v>10.28871594050657</v>
       </c>
       <c r="C3" t="n">
-        <v>28.02889695624643</v>
+        <v>22.39366513386975</v>
       </c>
       <c r="D3" t="n">
-        <v>18.42740440871263</v>
+        <v>24.1755372170777</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.13957240491907</v>
+        <v>6.44517367838031</v>
       </c>
       <c r="C4" t="n">
-        <v>42.12973923234337</v>
+        <v>12.76272015520853</v>
       </c>
       <c r="D4" t="n">
-        <v>21.19887817780138</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43723101043667</v>
+        <v>13.63145145187003</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12349932138352</v>
+        <v>73.77020785717897</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249943370618246</v>
+        <v>1.603700170808239</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.35288939418111</v>
+        <v>2.622248118043231</v>
       </c>
       <c r="C2" t="n">
-        <v>3.382120841130261</v>
+        <v>6.246860642122455</v>
       </c>
       <c r="D2" t="n">
-        <v>25.37621465937156</v>
+        <v>13.2045066221196</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.60612354861455</v>
+        <v>10.0481877529661</v>
       </c>
       <c r="C3" t="n">
-        <v>20.96522222419064</v>
+        <v>26.56118413839745</v>
       </c>
       <c r="D3" t="n">
-        <v>31.73008580125691</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.90603962449534</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="C4" t="n">
-        <v>58.36391926976863</v>
+        <v>39.98560224626834</v>
       </c>
       <c r="D4" t="n">
-        <v>25.67859295227957</v>
+        <v>28.29495058409733</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.05786636128833</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="C5" t="n">
-        <v>45.92124886614456</v>
+        <v>16.3460992757094</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2869166760141</v>
+        <v>27.56256679672921</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72446223347498</v>
+        <v>14.84710787558402</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0192196241973</v>
+        <v>87.43296860066143</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181115558368744</v>
+        <v>2.474517979264002</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.969827863075607</v>
+        <v>2.238384765682728</v>
       </c>
       <c r="C2" t="n">
-        <v>4.246058820867455</v>
+        <v>5.166938167450963</v>
       </c>
       <c r="D2" t="n">
-        <v>32.00399341074177</v>
+        <v>18.58153879827938</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.545836028028</v>
+        <v>9.52295273119406</v>
       </c>
       <c r="C3" t="n">
-        <v>16.49336143134641</v>
+        <v>25.43708301703486</v>
       </c>
       <c r="D3" t="n">
-        <v>43.95775345765094</v>
+        <v>33.90465696616359</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.70031457496002</v>
+        <v>17.43387573201486</v>
       </c>
       <c r="C4" t="n">
-        <v>55.10942563019046</v>
+        <v>55.50506995500192</v>
       </c>
       <c r="D4" t="n">
-        <v>35.25063306868597</v>
+        <v>36.55243052451725</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.14027641518284</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>78.2452920284708</v>
+        <v>50.29002615004288</v>
       </c>
       <c r="D5" t="n">
-        <v>32.37313054753858</v>
+        <v>31.857713002809</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24908617943821</v>
+        <v>6.883033154474389</v>
       </c>
       <c r="C6" t="n">
-        <v>43.59254331167113</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.040440980952</v>
+        <v>16.09870124482432</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6924006852583</v>
+        <v>101.6760078620484</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013480326983999</v>
+        <v>3.389200262068279</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.718901361415924</v>
+        <v>2.921681167838508</v>
       </c>
       <c r="C2" t="n">
-        <v>4.446335352533804</v>
+        <v>7.347399818583129</v>
       </c>
       <c r="D2" t="n">
-        <v>35.66591234758238</v>
+        <v>21.14193681095506</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3003991019663</v>
+        <v>8.51666133434108</v>
       </c>
       <c r="C3" t="n">
-        <v>15.4674350804085</v>
+        <v>22.24149423971149</v>
       </c>
       <c r="D3" t="n">
-        <v>55.03677630007619</v>
+        <v>40.89960935892212</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>18.13582534055133</v>
       </c>
       <c r="C4" t="n">
-        <v>39.65377152223292</v>
+        <v>60.2655645728947</v>
       </c>
       <c r="D4" t="n">
-        <v>42.41051907575796</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.18245050873644</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>66.73430019617695</v>
+        <v>79.57065142920399</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>37.89546138392689</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.18116566139593</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="C6" t="n">
-        <v>57.51961624411638</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>26.64954143177966</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.046340621979251</v>
+        <v>17.37966090069909</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05944333105548</v>
+        <v>115.574744989649</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403962888737031</v>
+        <v>4.344915225174773</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.577128781376882</v>
+        <v>3.214241983704057</v>
       </c>
       <c r="C2" t="n">
-        <v>3.439062207976577</v>
+        <v>9.011462177281473</v>
       </c>
       <c r="D2" t="n">
-        <v>35.26732277965817</v>
+        <v>17.81184859814988</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.25331626989146</v>
+        <v>9.248063374004955</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66516727958961</v>
+        <v>25.68742868161779</v>
       </c>
       <c r="D3" t="n">
-        <v>71.69703484114456</v>
+        <v>47.41350537659971</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.65827935012666</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="C4" t="n">
-        <v>39.15602543617979</v>
+        <v>57.16422357517902</v>
       </c>
       <c r="D4" t="n">
-        <v>61.41420938686347</v>
+        <v>54.06288257746336</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.68085954732433</v>
+        <v>24.12644983186537</v>
       </c>
       <c r="C5" t="n">
-        <v>70.17041716104079</v>
+        <v>96.38308086443064</v>
       </c>
       <c r="D5" t="n">
-        <v>38.77903431774902</v>
+        <v>45.25856916577796</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.58496706747763</v>
+        <v>20.60884780754905</v>
       </c>
       <c r="C6" t="n">
-        <v>86.2190468823634</v>
+        <v>89.76119259928589</v>
       </c>
       <c r="D6" t="n">
-        <v>34.09315252537899</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="C7" t="n">
-        <v>59.5272902993011</v>
+        <v>48.98724694650735</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>28.53940576245478</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264350740473261</v>
+        <v>18.68354754924593</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36763893241009</v>
+        <v>129.0054473638409</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448263055354945</v>
+        <v>5.338156442641694</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.94390151213769</v>
+        <v>2.839214360681776</v>
       </c>
       <c r="C2" t="n">
-        <v>2.507383636646354</v>
+        <v>5.406484607287184</v>
       </c>
       <c r="D2" t="n">
-        <v>34.87462369795945</v>
+        <v>13.91234671688155</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.62008900065226</v>
+        <v>12.15403657857551</v>
       </c>
       <c r="C3" t="n">
-        <v>14.69676313257475</v>
+        <v>40.63453747877548</v>
       </c>
       <c r="D3" t="n">
-        <v>83.27674901273569</v>
+        <v>52.78366531882975</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.43077592464865</v>
+        <v>11.58854990092935</v>
       </c>
       <c r="C4" t="n">
-        <v>40.66202641449439</v>
+        <v>84.87208903213676</v>
       </c>
       <c r="D4" t="n">
-        <v>83.54476613599506</v>
+        <v>52.95252592396021</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.40645321622075</v>
+        <v>11.60916660271853</v>
       </c>
       <c r="C5" t="n">
-        <v>71.44668917656163</v>
+        <v>53.62796834448203</v>
       </c>
       <c r="D5" t="n">
-        <v>52.05717201768713</v>
+        <v>37.20823799095412</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>99.34108669732626</v>
+        <v>32.24157635516951</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>26.00256969468102</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>95.15982322493909</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>55.66018609227291</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
         <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.469346514651497</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03014828982934</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53567820032006</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
